--- a/tests/Common_Test_Cases/公共用例_UI自动化.xlsx
+++ b/tests/Common_Test_Cases/公共用例_UI自动化.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Auto_Testing\UI-Smoke-Testing\tests\Common_Test_Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E243D7-752A-4EB7-957E-3472AB0107F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B752AF5-4C11-427C-835B-C01BC2A93913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="8940" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="23160" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="新增" sheetId="21" r:id="rId1"/>

--- a/tests/Common_Test_Cases/公共用例_UI自动化.xlsx
+++ b/tests/Common_Test_Cases/公共用例_UI自动化.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Auto_Testing\UI-Smoke-Testing\tests\Common_Test_Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B752AF5-4C11-427C-835B-C01BC2A93913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DA07B3-B607-4138-BABE-B119FE1DC50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="23160" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="新增" sheetId="21" r:id="rId1"/>
@@ -82,9 +82,6 @@
     <t>P1</t>
   </si>
   <si>
-    <t>ADD-004</t>
-  </si>
-  <si>
     <t>ADD-005</t>
   </si>
   <si>
@@ -1794,6 +1791,10 @@
   </si>
   <si>
     <t>用户已登录且拥有新增权限；已进入新增页面；页面加载完成；金额总长度上限为 20 位（含小数点，有小数点数值位19位）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADD-004</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2547,40 +2548,40 @@
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B2" s="14" t="s">
+        <v>479</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="14" t="s">
         <v>482</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="14" t="s">
+        <v>486</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>487</v>
-      </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="14" t="s">
         <v>484</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>485</v>
       </c>
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="15"/>
       <c r="M2" s="14" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>13</v>
@@ -2589,19 +2590,19 @@
         <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>15</v>
@@ -2612,7 +2613,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="7"/>
       <c r="M3" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1">
@@ -2623,22 +2624,22 @@
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>443</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>18</v>
@@ -2652,28 +2653,28 @@
     </row>
     <row r="5" spans="1:13" ht="42" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>19</v>
+        <v>559</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>15</v>
@@ -2687,28 +2688,28 @@
     </row>
     <row r="6" spans="1:13" ht="42" customHeight="1">
       <c r="A6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="F6" s="2">
         <v>123.123456</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>18</v>
@@ -2722,28 +2723,28 @@
     </row>
     <row r="7" spans="1:13" ht="42" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="D7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>18</v>
@@ -2754,33 +2755,33 @@
       <c r="K7" s="4"/>
       <c r="L7" s="7"/>
       <c r="M7" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="42" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F8" s="2">
         <v>9999999999999.9902</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>18</v>
@@ -2791,33 +2792,33 @@
       <c r="K8" s="4"/>
       <c r="L8" s="7"/>
       <c r="M8" s="8" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="42" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>18</v>
@@ -2831,28 +2832,28 @@
     </row>
     <row r="10" spans="1:13" ht="42" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="D10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>18</v>
@@ -2866,28 +2867,28 @@
     </row>
     <row r="11" spans="1:13" ht="42" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="D11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>18</v>
@@ -2901,31 +2902,31 @@
     </row>
     <row r="12" spans="1:13" ht="42" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="D12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>16</v>
@@ -2936,28 +2937,28 @@
     </row>
     <row r="13" spans="1:13" ht="42" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>18</v>
@@ -2971,28 +2972,28 @@
     </row>
     <row r="14" spans="1:13" ht="42" customHeight="1">
       <c r="A14" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="D14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>15</v>
@@ -3006,28 +3007,28 @@
     </row>
     <row r="15" spans="1:13" ht="42" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>18</v>
@@ -3041,28 +3042,28 @@
     </row>
     <row r="16" spans="1:13" ht="42" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>15</v>
@@ -3076,28 +3077,28 @@
     </row>
     <row r="17" spans="1:13" ht="42" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>15</v>
@@ -3111,28 +3112,28 @@
     </row>
     <row r="18" spans="1:13" ht="42" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>18</v>
@@ -3146,28 +3147,28 @@
     </row>
     <row r="19" spans="1:13" ht="42" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>18</v>
@@ -3181,28 +3182,28 @@
     </row>
     <row r="20" spans="1:13" ht="42" customHeight="1">
       <c r="A20" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="F20" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>18</v>
@@ -3216,28 +3217,28 @@
     </row>
     <row r="21" spans="1:13" ht="42" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>18</v>
@@ -3251,28 +3252,28 @@
     </row>
     <row r="22" spans="1:13" ht="42" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="12" t="s">
         <v>107</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>108</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>15</v>
@@ -3286,28 +3287,28 @@
     </row>
     <row r="23" spans="1:13" ht="42" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="12" t="s">
         <v>111</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>112</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>15</v>
@@ -3321,28 +3322,28 @@
     </row>
     <row r="24" spans="1:13" ht="89.35" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>18</v>
@@ -3356,28 +3357,28 @@
     </row>
     <row r="25" spans="1:13" ht="42" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>15</v>
@@ -3391,28 +3392,28 @@
     </row>
     <row r="26" spans="1:13" ht="42" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>18</v>
@@ -3426,31 +3427,31 @@
     </row>
     <row r="27" spans="1:13" ht="42" customHeight="1">
       <c r="A27" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="D27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="G27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="I27" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>16</v>
@@ -3458,33 +3459,33 @@
       <c r="K27" s="4"/>
       <c r="L27" s="7"/>
       <c r="M27" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="42" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>15</v>
@@ -3498,28 +3499,28 @@
     </row>
     <row r="29" spans="1:13" ht="42" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>15</v>
@@ -3533,28 +3534,28 @@
     </row>
     <row r="30" spans="1:13" ht="42" customHeight="1">
       <c r="A30" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="D30" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>18</v>
@@ -3568,28 +3569,28 @@
     </row>
     <row r="31" spans="1:13" ht="42" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>18</v>
@@ -3603,28 +3604,28 @@
     </row>
     <row r="32" spans="1:13" ht="42" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="12" t="s">
         <v>155</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>156</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>18</v>
@@ -3638,28 +3639,28 @@
     </row>
     <row r="33" spans="1:13" ht="42" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="G33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>15</v>
@@ -3673,28 +3674,28 @@
     </row>
     <row r="34" spans="1:13" ht="42" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="G34" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>18</v>
@@ -3708,28 +3709,28 @@
     </row>
     <row r="35" spans="1:13" ht="42" customHeight="1">
       <c r="A35" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="D35" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="G35" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>18</v>
@@ -3743,28 +3744,28 @@
     </row>
     <row r="36" spans="1:13" ht="42" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="G36" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>18</v>
@@ -3778,28 +3779,28 @@
     </row>
     <row r="37" spans="1:13" ht="42" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="G37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>18</v>
@@ -3813,28 +3814,28 @@
     </row>
     <row r="38" spans="1:13" ht="42" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="G38" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>18</v>
@@ -3848,28 +3849,28 @@
     </row>
     <row r="39" spans="1:13" ht="42" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="G39" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>15</v>
@@ -3883,31 +3884,31 @@
     </row>
     <row r="40" spans="1:13" ht="42" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="G40" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="I40" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>16</v>
@@ -3918,28 +3919,28 @@
     </row>
     <row r="41" spans="1:13" ht="42" customHeight="1">
       <c r="A41" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="D41" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="G41" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>18</v>
@@ -3953,28 +3954,28 @@
     </row>
     <row r="42" spans="1:13" ht="42" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="G42" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>18</v>
@@ -3988,31 +3989,31 @@
     </row>
     <row r="43" spans="1:13" ht="42" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H43" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>16</v>
@@ -4023,28 +4024,28 @@
     </row>
     <row r="44" spans="1:13" ht="42" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="G44" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>15</v>
@@ -4058,28 +4059,28 @@
     </row>
     <row r="45" spans="1:13" ht="42" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="G45" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="H45" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>18</v>
@@ -4093,28 +4094,28 @@
     </row>
     <row r="46" spans="1:13" ht="42" customHeight="1">
       <c r="A46" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="D46" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="F46" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="G46" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="H46" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>18</v>
@@ -4128,28 +4129,28 @@
     </row>
     <row r="47" spans="1:13" ht="42" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="H47" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>15</v>
@@ -4163,28 +4164,28 @@
     </row>
     <row r="48" spans="1:13" ht="42" customHeight="1">
       <c r="A48" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="F48" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="G48" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>18</v>
@@ -4198,28 +4199,28 @@
     </row>
     <row r="49" spans="1:13" ht="42" customHeight="1">
       <c r="A49" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D49" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="G49" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H49" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>15</v>
@@ -4233,28 +4234,28 @@
     </row>
     <row r="50" spans="1:13" ht="42" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="G50" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="H50" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>18</v>
@@ -4268,28 +4269,28 @@
     </row>
     <row r="51" spans="1:13" ht="42" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="G51" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="H51" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>15</v>
@@ -4303,28 +4304,28 @@
     </row>
     <row r="52" spans="1:13" ht="42" customHeight="1">
       <c r="A52" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="F52" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="G52" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="H52" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>18</v>
@@ -4338,28 +4339,28 @@
     </row>
     <row r="53" spans="1:13" ht="42" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="G53" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="H53" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>18</v>
@@ -4373,28 +4374,28 @@
     </row>
     <row r="54" spans="1:13" ht="42" customHeight="1">
       <c r="A54" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>268</v>
-      </c>
       <c r="D54" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="G54" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="H54" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>15</v>
@@ -4408,28 +4409,28 @@
     </row>
     <row r="55" spans="1:13" ht="42" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C55" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="F55" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="G55" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="H55" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>18</v>
@@ -4443,28 +4444,28 @@
     </row>
     <row r="56" spans="1:13" ht="42" customHeight="1">
       <c r="A56" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="C56" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="F56" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="G56" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="H56" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>18</v>
@@ -4478,28 +4479,28 @@
     </row>
     <row r="57" spans="1:13" ht="42" customHeight="1">
       <c r="A57" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="G57" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="H57" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>18</v>
@@ -4513,28 +4514,28 @@
     </row>
     <row r="58" spans="1:13" ht="42" customHeight="1">
       <c r="A58" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="G58" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="H58" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>15</v>
@@ -4548,28 +4549,28 @@
     </row>
     <row r="59" spans="1:13" ht="42" customHeight="1">
       <c r="A59" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="F59" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="G59" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="H59" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>18</v>
@@ -4583,31 +4584,31 @@
     </row>
     <row r="60" spans="1:13" ht="42" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="H60" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="H60" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="I60" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>16</v>
@@ -4618,28 +4619,28 @@
     </row>
     <row r="61" spans="1:13" ht="42" customHeight="1">
       <c r="A61" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="F61" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="G61" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="H61" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>18</v>
@@ -4653,28 +4654,28 @@
     </row>
     <row r="62" spans="1:13" ht="42" customHeight="1">
       <c r="A62" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="F62" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="G62" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="H62" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>325</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>15</v>
@@ -4688,28 +4689,28 @@
     </row>
     <row r="63" spans="1:13" ht="42" customHeight="1">
       <c r="A63" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="D63" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="F63" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="G63" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="H63" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>15</v>
@@ -4723,28 +4724,28 @@
     </row>
     <row r="64" spans="1:13" ht="42" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C64" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="F64" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F64" s="2" t="s">
+      <c r="G64" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="H64" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>18</v>
@@ -4758,28 +4759,28 @@
     </row>
     <row r="65" spans="1:13" ht="42" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="F65" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="G65" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="H65" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>18</v>
@@ -4793,28 +4794,28 @@
     </row>
     <row r="66" spans="1:13" ht="42" customHeight="1">
       <c r="A66" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="F66" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="G66" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="H66" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>18</v>
@@ -4828,28 +4829,28 @@
     </row>
     <row r="67" spans="1:13" ht="42" customHeight="1">
       <c r="A67" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="D67" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="E67" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="F67" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G67" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H67" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>18</v>
@@ -4863,28 +4864,28 @@
     </row>
     <row r="68" spans="1:13" ht="42" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="D68" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F68" s="2" t="s">
+      <c r="G68" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="H68" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>15</v>
@@ -4898,28 +4899,28 @@
     </row>
     <row r="69" spans="1:13" ht="42" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="D69" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="F69" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="G69" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="H69" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>15</v>
@@ -4933,28 +4934,28 @@
     </row>
     <row r="70" spans="1:13" ht="42" customHeight="1">
       <c r="A70" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="D70" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F70" s="2" t="s">
+      <c r="G70" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="H70" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
@@ -4964,61 +4965,61 @@
     </row>
     <row r="71" spans="1:13" ht="42" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="E71" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G71" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H71" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
       <c r="L71" s="7"/>
       <c r="M71" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="42" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="E72" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="F72" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="F72" s="2" t="s">
+      <c r="G72" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="H72" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
@@ -5028,28 +5029,28 @@
     </row>
     <row r="73" spans="1:13" ht="42" customHeight="1">
       <c r="A73" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="G73" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="H73" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>15</v>
@@ -5063,28 +5064,28 @@
     </row>
     <row r="74" spans="1:13" ht="42" customHeight="1">
       <c r="A74" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="G74" s="2" t="s">
+      <c r="H74" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>18</v>
@@ -5098,28 +5099,28 @@
     </row>
     <row r="75" spans="1:13" ht="42" customHeight="1">
       <c r="A75" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D75" s="2" t="s">
+      <c r="E75" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="G75" s="2" t="s">
+      <c r="H75" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>15</v>
@@ -5133,28 +5134,28 @@
     </row>
     <row r="76" spans="1:13" ht="42" customHeight="1">
       <c r="A76" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F76" s="2" t="s">
+      <c r="G76" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="H76" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>15</v>
@@ -5168,28 +5169,28 @@
     </row>
     <row r="77" spans="1:13" ht="42" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>373</v>
-      </c>
       <c r="D77" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>452</v>
-      </c>
       <c r="G77" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="H77" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
@@ -5199,61 +5200,61 @@
     </row>
     <row r="78" spans="1:13" ht="42" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>373</v>
-      </c>
       <c r="D78" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="G78" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="G78" s="2" t="s">
+      <c r="H78" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
       <c r="L78" s="7"/>
       <c r="M78" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="42" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="E79" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="F79" s="2" t="s">
+      <c r="G79" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="H79" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>15</v>
@@ -5267,28 +5268,28 @@
     </row>
     <row r="80" spans="1:13" ht="42" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="F80" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="G80" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="G80" s="3" t="s">
+      <c r="H80" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>18</v>
@@ -6180,61 +6181,61 @@
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B2" s="14" t="s">
+        <v>479</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>482</v>
-      </c>
       <c r="E2" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>501</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="14" t="s">
         <v>502</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="14" t="s">
         <v>503</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>504</v>
       </c>
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="15"/>
       <c r="M2" s="14" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>492</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
@@ -6244,28 +6245,28 @@
     </row>
     <row r="4" spans="1:13" ht="41.65">
       <c r="A4" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>403</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>15</v>
@@ -6279,28 +6280,28 @@
     </row>
     <row r="5" spans="1:13" ht="41.65">
       <c r="A5" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>428</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>18</v>
@@ -6314,28 +6315,28 @@
     </row>
     <row r="6" spans="1:13" ht="42" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -6345,28 +6346,28 @@
     </row>
     <row r="7" spans="1:13" ht="42" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>355</v>
-      </c>
       <c r="E7" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>411</v>
-      </c>
       <c r="G7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>18</v>
@@ -6380,28 +6381,28 @@
     </row>
     <row r="8" spans="1:13" ht="42" customHeight="1">
       <c r="A8" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>410</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>15</v>
@@ -6415,28 +6416,28 @@
     </row>
     <row r="9" spans="1:13" ht="42" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>15</v>
@@ -6450,61 +6451,61 @@
     </row>
     <row r="10" spans="1:13" ht="42" customHeight="1">
       <c r="A10" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>415</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="7"/>
       <c r="M10" s="8" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A11" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>417</v>
-      </c>
       <c r="F11" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>15</v>
@@ -6518,28 +6519,28 @@
     </row>
     <row r="12" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>373</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>411</v>
-      </c>
       <c r="G12" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>18</v>
@@ -6553,28 +6554,28 @@
     </row>
     <row r="13" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>373</v>
-      </c>
       <c r="D13" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>15</v>
@@ -6588,28 +6589,28 @@
     </row>
     <row r="14" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>15</v>
@@ -6623,28 +6624,28 @@
     </row>
     <row r="15" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>373</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -6654,61 +6655,61 @@
     </row>
     <row r="16" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>373</v>
-      </c>
       <c r="D16" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="7"/>
       <c r="M16" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="42" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>518</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>15</v>
@@ -6722,28 +6723,28 @@
     </row>
     <row r="18" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>18</v>
@@ -6840,61 +6841,61 @@
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B2" s="14" t="s">
+        <v>479</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>482</v>
-      </c>
       <c r="E2" s="14" t="s">
+        <v>507</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>508</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="14" t="s">
         <v>509</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="14" t="s">
         <v>510</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>511</v>
       </c>
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="15"/>
       <c r="M2" s="14" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>452</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
@@ -6904,28 +6905,28 @@
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -6935,28 +6936,28 @@
     </row>
     <row r="5" spans="1:13" ht="42" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>373</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>527</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -6966,28 +6967,28 @@
     </row>
     <row r="6" spans="1:13" ht="42" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="E6" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>15</v>
@@ -7001,28 +7002,28 @@
     </row>
     <row r="7" spans="1:13" ht="42" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>18</v>
@@ -7119,28 +7120,28 @@
     </row>
     <row r="2" spans="1:25" ht="42" customHeight="1">
       <c r="A2" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>530</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="C2" s="17" t="s">
         <v>531</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="D2" s="17" t="s">
+        <v>553</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>532</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>554</v>
-      </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>533</v>
       </c>
-      <c r="F2" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>534</v>
-      </c>
       <c r="H2" s="17" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>15</v>
@@ -7152,28 +7153,28 @@
     </row>
     <row r="3" spans="1:25" ht="42" customHeight="1">
       <c r="A3" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>530</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="C3" s="17" t="s">
         <v>531</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="D3" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>532</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>553</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="F3" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>533</v>
       </c>
-      <c r="F3" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>534</v>
-      </c>
       <c r="H3" s="17" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I3" s="18" t="s">
         <v>15</v>
@@ -7185,28 +7186,28 @@
     </row>
     <row r="4" spans="1:25" s="20" customFormat="1" ht="42" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>15</v>
@@ -7230,28 +7231,28 @@
     </row>
     <row r="5" spans="1:25" s="20" customFormat="1" ht="42" customHeight="1">
       <c r="A5" s="19" t="s">
+        <v>535</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>539</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>15</v>
@@ -7275,28 +7276,28 @@
     </row>
     <row r="6" spans="1:25" s="20" customFormat="1" ht="42" customHeight="1">
       <c r="A6" s="21" t="s">
+        <v>539</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>543</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>15</v>

--- a/tests/Common_Test_Cases/公共用例_UI自动化.xlsx
+++ b/tests/Common_Test_Cases/公共用例_UI自动化.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Auto_Testing\UI-Smoke-Testing\tests\Common_Test_Cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Auto_Testing\UI-Test-Automation\tests\Common_Test_Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DA07B3-B607-4138-BABE-B119FE1DC50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DD63A5-EB69-497A-BEF6-364D05CCBF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="579">
   <si>
     <t>用例ID</t>
   </si>
@@ -857,15 +857,6 @@
   </si>
   <si>
     <t>用户已登录且拥有新增权限；已进入新增页面；页面加载完成；存在至少三个复选项</t>
-  </si>
-  <si>
-    <t>选择 A、B、C</t>
-  </si>
-  <si>
-    <t>依次勾选三个选项并保存</t>
-  </si>
-  <si>
-    <t>三个选项均保持选中；保存后回显一致</t>
   </si>
   <si>
     <t>ADD-058</t>
@@ -1795,6 +1786,80 @@
   </si>
   <si>
     <t>ADD-004</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂存</t>
+  </si>
+  <si>
+    <t>暂存按钮</t>
+  </si>
+  <si>
+    <t>快速连续点击暂存 5 次</t>
+  </si>
+  <si>
+    <t>连续快速点击暂存按钮</t>
+  </si>
+  <si>
+    <t>点击暂存，查看编辑、详情页面</t>
+  </si>
+  <si>
+    <t>暂存反馈信息检查</t>
+  </si>
+  <si>
+    <t>点击暂存，查看按钮反馈信息</t>
+  </si>
+  <si>
+    <t>显示：暂存成功、操作成功等</t>
+  </si>
+  <si>
+    <t>新增暂存不要显示：提交成功、编辑成功等</t>
+  </si>
+  <si>
+    <t>暂存按钮</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂存不校验字段必填</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>清空所有必填项值</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击暂存按钮</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>不校验必填，成功保存</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADD-080</t>
+  </si>
+  <si>
+    <t>ADD-081</t>
+  </si>
+  <si>
+    <t>ADD-082</t>
+  </si>
+  <si>
+    <t>ADD-083</t>
+  </si>
+  <si>
+    <t>ADD-084</t>
+  </si>
+  <si>
+    <t>选择所有选项</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>依次勾选所有选项并保存</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有选项均保持选中；保存后回显一致</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2208,8 +2273,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OptimizedAddCases3" displayName="OptimizedAddCases3" ref="A1:M133" totalsRowShown="0">
-  <autoFilter ref="A1:M133" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OptimizedAddCases3" displayName="OptimizedAddCases3" ref="A1:M138" totalsRowShown="0">
+  <autoFilter ref="A1:M138" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="用例ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="功能"/>
@@ -2487,7 +2552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M133"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2548,40 +2613,40 @@
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B2" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>477</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>478</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="F2" s="14" t="s">
+        <v>483</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="H2" s="14" t="s">
         <v>481</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>482</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>486</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>483</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>484</v>
       </c>
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="15"/>
       <c r="M2" s="14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>13</v>
@@ -2590,19 +2655,19 @@
         <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>15</v>
@@ -2613,7 +2678,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="7"/>
       <c r="M3" s="8" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1">
@@ -2624,22 +2689,22 @@
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>445</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>18</v>
@@ -2653,7 +2718,7 @@
     </row>
     <row r="5" spans="1:13" ht="42" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>20</v>
@@ -2674,7 +2739,7 @@
         <v>25</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>15</v>
@@ -2694,7 +2759,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
@@ -2706,7 +2771,7 @@
         <v>123.123456</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>29</v>
@@ -2735,7 +2800,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>32</v>
@@ -2772,13 +2837,13 @@
         <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="F8" s="2">
         <v>9999999999999.9902</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>39</v>
@@ -2792,7 +2857,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="7"/>
       <c r="M8" s="8" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="42" customHeight="1">
@@ -2952,7 +3017,7 @@
         <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>65</v>
@@ -2987,7 +3052,7 @@
         <v>64</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>69</v>
@@ -3013,7 +3078,7 @@
         <v>20</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>74</v>
@@ -3042,13 +3107,13 @@
     </row>
     <row r="16" spans="1:13" ht="42" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>80</v>
@@ -3083,7 +3148,7 @@
         <v>20</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>84</v>
@@ -3118,7 +3183,7 @@
         <v>20</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>74</v>
@@ -3153,7 +3218,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>80</v>
@@ -3188,7 +3253,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>84</v>
@@ -3223,7 +3288,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>74</v>
@@ -3258,7 +3323,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>80</v>
@@ -3293,7 +3358,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>84</v>
@@ -3328,7 +3393,7 @@
         <v>20</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>113</v>
@@ -3337,7 +3402,7 @@
         <v>114</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>115</v>
@@ -4339,7 +4404,7 @@
     </row>
     <row r="53" spans="1:13" ht="42" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>20</v>
@@ -4424,13 +4489,13 @@
         <v>277</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>278</v>
+        <v>576</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>279</v>
+        <v>577</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>280</v>
+        <v>578</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>18</v>
@@ -4453,19 +4518,19 @@
         <v>275</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="H56" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>18</v>
@@ -4485,22 +4550,22 @@
         <v>266</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="G57" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="H57" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>18</v>
@@ -4520,22 +4585,22 @@
         <v>266</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="H58" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>15</v>
@@ -4549,28 +4614,28 @@
     </row>
     <row r="59" spans="1:13" ht="42" customHeight="1">
       <c r="A59" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>266</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="H59" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>18</v>
@@ -4584,28 +4649,28 @@
     </row>
     <row r="60" spans="1:13" ht="42" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>266</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="H60" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>60</v>
@@ -4619,28 +4684,28 @@
     </row>
     <row r="61" spans="1:13" ht="42" customHeight="1">
       <c r="A61" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>266</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="H61" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>18</v>
@@ -4654,28 +4719,28 @@
     </row>
     <row r="62" spans="1:13" ht="42" customHeight="1">
       <c r="A62" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>266</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="H62" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>15</v>
@@ -4689,28 +4754,28 @@
     </row>
     <row r="63" spans="1:13" ht="42" customHeight="1">
       <c r="A63" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>266</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="H63" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>15</v>
@@ -4724,28 +4789,28 @@
     </row>
     <row r="64" spans="1:13" ht="42" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>266</v>
       </c>
       <c r="C64" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="G64" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="H64" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>18</v>
@@ -4759,28 +4824,28 @@
     </row>
     <row r="65" spans="1:13" ht="42" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>266</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="H65" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>18</v>
@@ -4794,28 +4859,28 @@
     </row>
     <row r="66" spans="1:13" ht="42" customHeight="1">
       <c r="A66" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>266</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="G66" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="H66" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>18</v>
@@ -4829,31 +4894,31 @@
     </row>
     <row r="67" spans="1:13" ht="42" customHeight="1">
       <c r="A67" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>352</v>
+        <v>557</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>353</v>
+        <v>566</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>354</v>
+        <v>567</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>451</v>
+        <v>568</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>357</v>
+        <v>569</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>358</v>
+        <v>570</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>16</v>
@@ -4864,28 +4929,28 @@
     </row>
     <row r="68" spans="1:13" ht="42" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>352</v>
+        <v>557</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>353</v>
+        <v>558</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>361</v>
+        <v>559</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>362</v>
+        <v>560</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>15</v>
@@ -4899,158 +4964,158 @@
     </row>
     <row r="69" spans="1:13" ht="42" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>352</v>
+        <v>557</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>353</v>
+        <v>558</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>365</v>
+        <v>447</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>367</v>
+        <v>448</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>368</v>
+        <v>561</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>16</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
       <c r="K69" s="4"/>
       <c r="L69" s="7"/>
       <c r="M69" s="8"/>
     </row>
     <row r="70" spans="1:13" ht="42" customHeight="1">
       <c r="A70" s="6" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>352</v>
+        <v>557</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>353</v>
+        <v>558</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>450</v>
+        <v>562</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>452</v>
+        <v>563</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>453</v>
+        <v>564</v>
       </c>
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
       <c r="L70" s="7"/>
-      <c r="M70" s="8"/>
+      <c r="M70" s="8" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="71" spans="1:13" ht="42" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>457</v>
+        <v>557</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>353</v>
+        <v>558</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>366</v>
+        <v>462</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>454</v>
+        <v>561</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
       <c r="L71" s="7"/>
-      <c r="M71" s="8" t="s">
-        <v>456</v>
-      </c>
+      <c r="M71" s="8"/>
     </row>
     <row r="72" spans="1:13" ht="42" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>457</v>
+        <v>349</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>463</v>
+        <v>350</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>464</v>
+        <v>351</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>465</v>
+        <v>352</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>452</v>
+        <v>354</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
+        <v>355</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K72" s="4"/>
       <c r="L72" s="7"/>
       <c r="M72" s="8"/>
     </row>
     <row r="73" spans="1:13" ht="42" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>15</v>
@@ -5064,31 +5129,31 @@
     </row>
     <row r="74" spans="1:13" ht="42" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>16</v>
@@ -5099,98 +5164,92 @@
     </row>
     <row r="75" spans="1:13" ht="42" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>382</v>
+        <v>447</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>356</v>
+        <v>448</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>383</v>
+        <v>449</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I75" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>16</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
       <c r="K75" s="4"/>
       <c r="L75" s="7"/>
       <c r="M75" s="8"/>
     </row>
     <row r="76" spans="1:13" ht="42" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>365</v>
+        <v>455</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>386</v>
+        <v>448</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>387</v>
+        <v>451</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>16</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
       <c r="K76" s="4"/>
       <c r="L76" s="7"/>
-      <c r="M76" s="8"/>
+      <c r="M76" s="8" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="77" spans="1:13" ht="42" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>371</v>
+        <v>454</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>372</v>
+        <v>460</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>366</v>
+        <v>462</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
@@ -5200,64 +5259,66 @@
     </row>
     <row r="78" spans="1:13" ht="42" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="F78" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>451</v>
-      </c>
       <c r="G78" s="2" t="s">
-        <v>460</v>
+        <v>373</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
+        <v>374</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K78" s="4"/>
       <c r="L78" s="7"/>
-      <c r="M78" s="8" t="s">
-        <v>462</v>
-      </c>
+      <c r="M78" s="8"/>
     </row>
     <row r="79" spans="1:13" ht="42" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>516</v>
+        <v>368</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>517</v>
+        <v>369</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>518</v>
+        <v>351</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>391</v>
+        <v>352</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>16</v>
@@ -5268,63 +5329,99 @@
     </row>
     <row r="80" spans="1:13" ht="42" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="I80" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J80" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K80" s="5"/>
-      <c r="L80" s="10"/>
-      <c r="M80" s="11"/>
+        <v>486</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K80" s="4"/>
+      <c r="L80" s="7"/>
+      <c r="M80" s="8"/>
     </row>
     <row r="81" spans="1:13" ht="42" customHeight="1">
-      <c r="A81" s="6"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
+      <c r="A81" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K81" s="4"/>
       <c r="L81" s="7"/>
       <c r="M81" s="8"/>
     </row>
     <row r="82" spans="1:13" ht="42" customHeight="1">
-      <c r="A82" s="6"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
+      <c r="A82" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>468</v>
+      </c>
       <c r="I82" s="4"/>
       <c r="J82" s="4"/>
       <c r="K82" s="4"/>
@@ -5332,49 +5429,107 @@
       <c r="M82" s="8"/>
     </row>
     <row r="83" spans="1:13" ht="42" customHeight="1">
-      <c r="A83" s="6"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
+      <c r="A83" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
       <c r="L83" s="7"/>
-      <c r="M83" s="8"/>
+      <c r="M83" s="8" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="84" spans="1:13" ht="42" customHeight="1">
-      <c r="A84" s="6"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
+      <c r="A84" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K84" s="4"/>
       <c r="L84" s="7"/>
       <c r="M84" s="8"/>
     </row>
     <row r="85" spans="1:13" ht="42" customHeight="1">
-      <c r="A85" s="6"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="7"/>
-      <c r="M85" s="8"/>
+      <c r="A85" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K85" s="5"/>
+      <c r="L85" s="10"/>
+      <c r="M85" s="11"/>
     </row>
     <row r="86" spans="1:13" ht="42" customHeight="1">
       <c r="A86" s="6"/>
@@ -6082,32 +6237,107 @@
       <c r="M132" s="8"/>
     </row>
     <row r="133" spans="1:13" ht="42" customHeight="1">
-      <c r="A133" s="9"/>
-      <c r="B133" s="3"/>
-      <c r="C133" s="3"/>
-      <c r="D133" s="3"/>
-      <c r="E133" s="3"/>
-      <c r="F133" s="3"/>
-      <c r="G133" s="3"/>
-      <c r="H133" s="3"/>
-      <c r="I133" s="5"/>
-      <c r="J133" s="5"/>
-      <c r="K133" s="5"/>
-      <c r="L133" s="10"/>
-      <c r="M133" s="11"/>
+      <c r="A133" s="6"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+      <c r="I133" s="4"/>
+      <c r="J133" s="4"/>
+      <c r="K133" s="4"/>
+      <c r="L133" s="7"/>
+      <c r="M133" s="8"/>
+    </row>
+    <row r="134" spans="1:13" ht="42" customHeight="1">
+      <c r="A134" s="6"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+      <c r="I134" s="4"/>
+      <c r="J134" s="4"/>
+      <c r="K134" s="4"/>
+      <c r="L134" s="7"/>
+      <c r="M134" s="8"/>
+    </row>
+    <row r="135" spans="1:13" ht="42" customHeight="1">
+      <c r="A135" s="6"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="2"/>
+      <c r="H135" s="2"/>
+      <c r="I135" s="4"/>
+      <c r="J135" s="4"/>
+      <c r="K135" s="4"/>
+      <c r="L135" s="7"/>
+      <c r="M135" s="8"/>
+    </row>
+    <row r="136" spans="1:13" ht="42" customHeight="1">
+      <c r="A136" s="6"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+      <c r="I136" s="4"/>
+      <c r="J136" s="4"/>
+      <c r="K136" s="4"/>
+      <c r="L136" s="7"/>
+      <c r="M136" s="8"/>
+    </row>
+    <row r="137" spans="1:13" ht="42" customHeight="1">
+      <c r="A137" s="6"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+      <c r="I137" s="4"/>
+      <c r="J137" s="4"/>
+      <c r="K137" s="4"/>
+      <c r="L137" s="7"/>
+      <c r="M137" s="8"/>
+    </row>
+    <row r="138" spans="1:13" ht="42" customHeight="1">
+      <c r="A138" s="9"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="5"/>
+      <c r="J138" s="5"/>
+      <c r="K138" s="5"/>
+      <c r="L138" s="10"/>
+      <c r="M138" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="J1:J133">
+  <conditionalFormatting sqref="J1:J138">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="通过"/>
     <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="失败"/>
     <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="阻塞"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="J1:J133" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="J1:J138" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"未执行,通过,失败,阻塞"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I1:I133" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" sqref="I1:I138" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"P0,P1,P2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6181,61 +6411,61 @@
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E2" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>498</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>500</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>501</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>502</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>503</v>
       </c>
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="15"/>
       <c r="M2" s="14" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
@@ -6245,28 +6475,28 @@
     </row>
     <row r="4" spans="1:13" ht="41.65">
       <c r="A4" s="6" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>496</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>15</v>
@@ -6280,28 +6510,28 @@
     </row>
     <row r="5" spans="1:13" ht="41.65">
       <c r="A5" s="6" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>18</v>
@@ -6315,28 +6545,28 @@
     </row>
     <row r="6" spans="1:13" ht="42" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -6346,28 +6576,28 @@
     </row>
     <row r="7" spans="1:13" ht="42" customHeight="1">
       <c r="A7" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>357</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>18</v>
@@ -6381,28 +6611,28 @@
     </row>
     <row r="8" spans="1:13" ht="42" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>15</v>
@@ -6416,28 +6646,28 @@
     </row>
     <row r="9" spans="1:13" ht="42" customHeight="1">
       <c r="A9" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>368</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>15</v>
@@ -6451,61 +6681,61 @@
     </row>
     <row r="10" spans="1:13" ht="42" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="7"/>
       <c r="M10" s="8" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>376</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>15</v>
@@ -6519,28 +6749,28 @@
     </row>
     <row r="12" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>18</v>
@@ -6554,28 +6784,28 @@
     </row>
     <row r="13" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>15</v>
@@ -6589,28 +6819,28 @@
     </row>
     <row r="14" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>15</v>
@@ -6624,28 +6854,28 @@
     </row>
     <row r="15" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -6655,61 +6885,61 @@
     </row>
     <row r="16" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="7"/>
       <c r="M16" s="8" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="42" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>15</v>
@@ -6723,28 +6953,28 @@
     </row>
     <row r="18" spans="1:13" ht="42" hidden="1" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>399</v>
-      </c>
       <c r="H18" s="3" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>18</v>
@@ -6841,61 +7071,61 @@
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E2" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>507</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>508</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>510</v>
       </c>
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="15"/>
       <c r="M2" s="14" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
@@ -6905,28 +7135,28 @@
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -6936,28 +7166,28 @@
     </row>
     <row r="5" spans="1:13" ht="42" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -6967,28 +7197,28 @@
     </row>
     <row r="6" spans="1:13" ht="42" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>15</v>
@@ -7002,28 +7232,28 @@
     </row>
     <row r="7" spans="1:13" ht="42" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>18</v>
@@ -7120,28 +7350,28 @@
     </row>
     <row r="2" spans="1:25" ht="42" customHeight="1">
       <c r="A2" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>550</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>529</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="F2" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>530</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>531</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>553</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>532</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>533</v>
-      </c>
       <c r="H2" s="17" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>15</v>
@@ -7153,28 +7383,28 @@
     </row>
     <row r="3" spans="1:25" ht="42" customHeight="1">
       <c r="A3" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>529</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="F3" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>530</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>531</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>552</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>532</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>533</v>
-      </c>
       <c r="H3" s="17" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="I3" s="18" t="s">
         <v>15</v>
@@ -7186,28 +7416,28 @@
     </row>
     <row r="4" spans="1:25" s="20" customFormat="1" ht="42" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>533</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>15</v>
@@ -7231,28 +7461,28 @@
     </row>
     <row r="5" spans="1:25" s="20" customFormat="1" ht="42" customHeight="1">
       <c r="A5" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>15</v>
@@ -7276,28 +7506,28 @@
     </row>
     <row r="6" spans="1:25" s="20" customFormat="1" ht="42" customHeight="1">
       <c r="A6" s="21" t="s">
+        <v>536</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>542</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>15</v>
